--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -7,10 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parking Lot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPEN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLOSED" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parking Lot'!$A$1:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,62 +463,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Effort</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Effort</t>
+          <t>Importance</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Importance</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -523,27 +521,22 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>v0.6 source-grounded rebuild of all 4 accreditor columns</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>v0.6 source-grounded rebuild of all 4 accreditor columns</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
           <t>Open. Multi-hour subagent fan-out work.</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>AABB ids in aabbRequirements.ts (138/168 marked "real") and
 COLA ids in colaRequirements.ts (167/168 marked "real") came from
@@ -553,13 +546,13 @@
 and TJC (CAMLAB PDF + text extract).</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>prior session handoff. Re-confirmed during 2026-05-01 QC
 review.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Pre-COLA. May 6-8 conference; Saturday + Sunday +
 Monday available before the booth.
@@ -570,20 +563,15 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>New flagship module: VeritaResponse (post-survey deficiency response)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>New flagship module: VeritaResponse (post-survey deficiency response)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Open. Decision to build = Yes. Sequencing = Decide
 later. User explicitly chose "decide later — just park for now" on
@@ -591,9 +579,9 @@
 is cleare...</t>
         </is>
       </c>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>A new module that helps a lab manage the full lifecycle of
 responding to inspection deficiencies (CAP, TJC, COLA, CMS-2567,
@@ -604,7 +592,7 @@
 complete the compliance lifecycle: prevent → respond → prove.</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 conference user request, COLA Nashville. User
 asked for thoughts and recommendations on adding a deficiency-response
@@ -612,7 +600,7 @@
 COLA, CMS-2567, AABB. URLs cited above.</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. Build is multi-week regardless;
 zero rationale for any code change before the conference ends.</t>
@@ -622,20 +610,15 @@
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Unregulated analyte / Alternative Assessment (AAA) coverage — cross-module gap</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Unregulated analyte / Alternative Assessment (AAA) coverage — cross-module gap</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>PARTIAL as of 2026-05-10.
 - Phase 1 (VeritaScan AAA sub-block, items 169-173) CLOSED via
@@ -643,16 +626,16 @@
  AAA gateway; new 5-item block uses ids 16...</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>**STATUS (as of 2026-05-22): Phases 1 and 2 SHIPPED. Phase 3 deferred
 behind #17 (VeritaResponse, not yet built).**</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. Phase 1 and Phase 2 data layer
 shipped 2026-05-10.
@@ -663,29 +646,24 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Live QC engine (Levey-Jennings + Westgard)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Live QC engine (Levey-Jennings + Westgard)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Open. Scoping doc required per Section 8 Process Rules
 ("Large tasks: present a build breakdown first, get approval, THEN
 build") before any code.</t>
         </is>
       </c>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>A daily-use QC workflow: Levey-Jennings charts, Westgard
 multi-rule violation detection, control lot management, automated QC
@@ -695,13 +673,13 @@
 pick the tool that draws their L-J chart.</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io),
 2026-05-10. Operator forwarded the analysis; no decision yet.</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. Multi-week scoping + multi-month
 v1 build. Comparable in scale to VeritaResponse (#17).
@@ -712,28 +690,23 @@
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>CMS-116 application support + state licensing tracking</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>CMS-116 application support + state licensing tracking</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Open. Small build relative to the other competitor-driven
 candidates. Useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>CMS-116 is the federal CLIA application form. Today
 VeritaPolicy covers ongoing CLIA posture but not the application
@@ -743,13 +716,13 @@
 CLIA.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io),
 2026-05-10. myLabCompliance.io has this; VeritaAssure does not.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. ~1-2 weeks for v1 (CMS-116 form +
 top-10-state licensure registry).
@@ -760,27 +733,22 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>Acquire CAP MOL (Molecular) checklist to verify 2 pending entries</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Acquire CAP MOL (Molecular) checklist to verify 2 pending entries</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
           <t>Open, blocks on operator obtaining the MOL checklist.</t>
         </is>
       </c>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>PR #108 left 2 entries in server/capRequirements.ts
 flagged as unverified because the operator does not hold the CAP MOL
@@ -794,13 +762,13 @@
 The MOL module's MAS xlsx is the only one missing from that set.</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>PR #108 commit 92f9573 (closed via merge 2026-05-11),
 audit findings.</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. Two entries; low traffic.
 ---</t>
@@ -810,29 +778,24 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Acquire AABB Standards 35th edition + current COLA Accreditation Manual for exhaustive citation verification</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Acquire AABB Standards 35th edition + current COLA Accreditation Manual for exhaustive citation verification</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Open, blocks on operator obtaining the gated accreditor
 manuals. Until then, AABB / COLA citations are best-effort against
 the public-source compilations.</t>
         </is>
       </c>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>The 2026-05-11 QC audit found that VeritaScan, cfrRequirements
 cross-refs, and colaRequirements.ts cite about 180 AABB and COLA codes
@@ -852,14 +815,14 @@
  does not enumerate fully.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 QC/QA audit, documented in
 OneDrive\Lab\Regulatory\aaa Truth Master Document\PROVENANCE.md
 "Audit-coverage limits" section.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. Operator-side action item, no code
 work pending until the source documents land.
@@ -870,28 +833,23 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>VeritaStock barcode scanning (full mobile scan flow)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>VeritaStock barcode scanning (full mobile scan flow)</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
           <t>Parked pending first paid commitment.
 ---</t>
         </is>
       </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>The remaining barcode-scanning build for VeritaStock, scoped
 during the 2026-05-20 Pfizer follow-up discussion. Order-now reorder
@@ -900,7 +858,7 @@
 Services-class inventory product.</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>2026-05-20 Pfizer follow-up session, after the order-now
 reorder document shipped (PR #286). Strategic decision documented in
@@ -911,28 +869,23 @@
 barcode scanning waits on revenue...</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
           <t>Plain-language summary layer for verbatim CFR citations</t>
         </is>
       </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>server/cfrRequirements.ts carries verbatim eCFR text in
 the description field (PR #301 closed #26). The verbatim text is
@@ -941,8 +894,8 @@
 director read faster.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency. Operator
 has not yet authorized a redesign attempt as of 2026-05-21.
@@ -953,23 +906,18 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
           <t>Lab leader community / forum (paid subscription idea)</t>
         </is>
       </c>
+      <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Operator-floated 2026-05-22: a vetted online forum for
 laboratory leaders (directors, managers, supervisors). Pricing as
@@ -982,8 +930,8 @@
 lab-leader water cooler.</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency.
 ---</t>
@@ -993,37 +941,32 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Active vs view-only seat split</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Active vs view-only seat split</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
           <t>Open. Real product change, ~1 week of engineering when prioritized. Not blocking any current customer; activate when a prospect explicitly asks "do you charge for our medical director?"</t>
         </is>
       </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>The pricing analysis doc (2026-05-21 MEDIUM scenario, Decision 3) proposed splitting seats into two types: active (techs, supervisors, lab managers who edit data; counted against the tier seat cap) and view-only (medical director, administrators, reviewers who sign but don't enter; unlimited and free on every tier). The current schema treats all seats as one bucket.</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The pricing analysis doc (2026-05-21 MEDIUM scenario, Decision 3) proposed splitting seats into two types: active (techs, supervisors, lab managers who edit data; counted against the tier seat cap) and view-only (medical director, administrators, reviewers who sign but don't enter; unlimited and free on every tier). The current schema treats all seats as one bucket.</t>
+          <t>Pricing analysis doc Decision 3 (2026-05-21); deferred during Phase B Stripe wiring (2026-05-23) because no current customer is constrained by the missing distinction.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Pricing analysis doc Decision 3 (2026-05-21); deferred during Phase B Stripe wiring (2026-05-23) because no current customer is constrained by the missing distinction.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. Quality-of-life for sales positioning, not table stakes.
 ---</t>
@@ -1033,37 +976,32 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>CCL lab name visual disambiguation in lab switcher</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>CCL lab name visual disambiguation in lab switcher</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
           <t>Open. Cosmetic. Only matters if Lisa reports picking the wrong lab from the dropdown.</t>
         </is>
       </c>
+      <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Lisa Veri's two labs both carry "UMass Memorial Health - Milford Regional Medical Center" with the secondary differentiated only by a trailing " CCL" suffix. The NavBar LabSwitcher dropdown truncates long names, which makes fast visual differentiation between her two labs harder than it should be.</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Lisa Veri's two labs both carry "UMass Memorial Health - Milford Regional Medical Center" with the secondary differentiated only by a trailing " CCL" suffix. The NavBar LabSwitcher dropdown truncates long names, which makes fast visual differentiation between her two labs harder than it should be.</t>
+          <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab via /api/admin/update-lab.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab via /api/admin/update-lab.</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Post-COLA.
 ---</t>
@@ -1073,96 +1011,148 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>VC Unlimited Y1/Y2 price disclosure UX</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VC Unlimited Y1/Y2 price disclosure UX</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
           <t>Open as a tracking item, not a build item. Trigger to act = first customer complaint or first procurement question that suggests the disclosure was missed.</t>
         </is>
       </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>VC Unlimited list pricing is $299 first year, $499/yr after (auto-applied VCFIRSTYEAR coupon delivers Y1 = $299; Y2+ renews at the underlying $499 base). The /pricing tile shows this in the period text ("$299 first year · $499/yr after") at text-base font-medium weight as of 2026-05-23.</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>VC Unlimited list pricing is $299 first year, $499/yr after (auto-applied VCFIRSTYEAR coupon delivers Y1 = $299; Y2+ renews at the underlying $499 base). The /pricing tile shows this in the period text ("$299 first year · $499/yr after") at text-base font-medium weight as of 2026-05-23.</t>
+          <t>Pricing rebuild 2026-05-23; flagged at the time as a potential UX gap pending customer feedback.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Pricing rebuild 2026-05-23; flagged at the time as a potential UX gap pending customer feedback.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
           <t>Post-COLA.
 ---</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+  </sheetData>
+  <autoFilter ref="A1:H14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1175,7 +1165,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1183,129 +1173,109 @@
 ---</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: site-wide search confirmed all surveyor language
 is past-tense, consistent with user's 2021-2025 service. User closed
 the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
 /api/my-studies/export. server/routes.ts line 1491 implements the
 endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: no ghp_* or github_pat_* patterns in current
 SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -1314,34 +1284,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -1352,35 +1317,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -1390,69 +1350,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -1467,34 +1417,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -1502,34 +1447,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -1544,66 +1484,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -1621,74 +1551,64 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
 features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaCheck™ already ships the Precision /
 Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
@@ -1696,28 +1616,23 @@
 ---</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
@@ -1725,34 +1640,29 @@
 shipped:</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -1763,7 +1673,7 @@
 page.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -1771,28 +1681,23 @@
 ---</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -1803,7 +1708,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -1811,28 +1716,23 @@
 ---</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -1843,7 +1743,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -1852,28 +1752,23 @@
 ---</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -1886,7 +1781,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -1895,35 +1790,30 @@
 ---</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -1932,124 +1822,171 @@
 ---</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H23"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Mini-LIS module (formerly #24) — HIPAA boundary</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Rejected 2026-05-21 by operator decision.</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 strategic decision (this session).
 ---</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Phlebotomy module (formerly #25) — HIPAA boundary</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Rejected 2026-05-21 by operator decision, same basis as R4.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2026-05-21 strategic decision (this session).
 ---</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>WSLH PT booth follow-up email (formerly #16) — stale</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Closed 2026-05-21 by operator decision.</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 cleanup decision (this session).
 ---</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Rotate Railway token because it appeared in chat</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Reason: Per session 299e9a73 turn 7 (and STANDING_REQUIREMENTS.md
 "CREDENTIAL HANDLING" section): tokens the user pastes in our chat are
@@ -2059,34 +1996,29 @@
 repo, which is an actual leak. Token-in-our-conversation is not.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 7, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Real Stripe checkout abandonment diagnostic (formerly #2)</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Reason: Operator decision 2026-05-10 — abandoned. Not pursuing a
 Stripe-session-based abandonment diagnostic. The original concern
@@ -2094,34 +2026,29 @@
 as a class of error to avoid; the build itself is no longer wanted.</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>VeritaScan sign-off date field (formerly #9)</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Reason: Operator clarification 2026-05-10 — VeritaScan sign-off
 is not a regulatory requirement. The cross-reference value with
@@ -2129,16 +2056,16 @@
 does not justify adding the schema and UI. No code change.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I42"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -534,8 +534,16 @@
           <t>Open. Multi-hour subagent fan-out work.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>L (3-5 weeks)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>High — accreditor citation accuracy underpins every VeritaPolicy / VeritaScan...</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>AABB ids in aabbRequirements.ts (138/168 marked "real") and
@@ -579,8 +587,16 @@
 is cleare...</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>XL (6+ weeks; flagship-scale)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>High — booth-validated demand at COLA Nashville; no existing module covers po...</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>A new module that helps a lab manage the full lifecycle of
@@ -626,12 +642,20 @@
  AAA gateway; new 5-item block uses ids 16...</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>S (1-3 days once #17 ships) for Phase 3 — Phases 1 and 2 already shipped.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Medium — closes a real workflow loop (AAA failure → VeritaResponse finding) b...</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>**STATUS (as of 2026-05-22): Phases 1 and 2 SHIPPED. Phase 3 deferred
-behind #17 (VeritaResponse, not yet built).**</t>
+          <t>Effort: S (1-3 days once #17 ships) for Phase 3 — Phases 1 and 2 already shipped.
+Importance: Medium — closes a real workflow loop (AAA failure → VeritaResponse finding) but only matters once #17 exists.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -661,8 +685,16 @@
 build") before any code.</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>XL (6+ weeks; flagship-scale)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>A daily-use QC workflow: Levey-Jennings charts, Westgard
@@ -704,8 +736,16 @@
 candidates. Useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>M (1-2 weeks for v1)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Medium — competitor (myLabCompliance.io) has this; useful at lab startup and...</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>CMS-116 is the federal CLIA application form. Today
@@ -746,8 +786,16 @@
           <t>Open, blocks on operator obtaining the MOL checklist.</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>N/A (operator action — ~1 hour of code work once the file is in hand)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Low — two entries total; low traffic; only matters when a customer cites a MO...</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>PR #108 left 2 entries in server/capRequirements.ts
@@ -793,8 +841,16 @@
 the public-source compilations.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>N/A (operator action — ~1-2 days of audit re-run once the manuals are held)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>High — gates #5 from reaching "exhaustively verified" status for AABB and COLA.</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>The 2026-05-11 QC audit found that VeritaScan, cfrRequirements
@@ -847,8 +903,16 @@
 ---</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>L (12 working days, ~3 weeks calendar)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>High — strategic moat vs Unity Lab Services ($30K+/yr); presold as included o...</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>The remaining barcode-scanning build for VeritaStock, scoped
@@ -883,8 +947,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>M (multi-day content authoring across 96 Master List rows if redesigned corre...</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Medium — director readability win; no customer urgency.</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>server/cfrRequirements.ts carries verbatim eCFR text in
@@ -915,8 +987,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>XL (ongoing operational commitment, not a build) as paid; S (a few days to sp...</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Low as paid product (SWOT verdict: don't build); Medium as free lead-funnel a...</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Operator-floated 2026-05-22: a vetted online forum for
@@ -954,8 +1034,16 @@
           <t>Open. Real product change, ~1 week of engineering when prioritized. Not blocking any current customer; activate when a prospect explicitly asks "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>M (~1 week of engineering when prioritized)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Medium — quality-of-life for sales positioning; /pricing copy already claims...</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>The pricing analysis doc (2026-05-21 MEDIUM scenario, Decision 3) proposed splitting seats into two types: active (techs, supervisors, lab managers who edit data; counted against the tier seat cap) and view-only (medical director, administrators, reviewers who sign but don't enter; unlimited and free on every tier). The current schema treats all seats as one bucket.</t>
@@ -989,8 +1077,16 @@
           <t>Open. Cosmetic. Only matters if Lisa reports picking the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>XS (under 1 day)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Low — cosmetic; only matters if Lisa picks the wrong lab from the dropdown.</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Lisa Veri's two labs both carry "UMass Memorial Health - Milford Regional Medical Center" with the secondary differentiated only by a trailing " CCL" suffix. The NavBar LabSwitcher dropdown truncates long names, which makes fast visual differentiation between her two labs harder than it should be.</t>
@@ -1024,8 +1120,16 @@
           <t>Open as a tracking item, not a build item. Trigger to act = first customer complaint or first procurement question that suggests the disclosure was missed.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>XS (under 1 day if triggered)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Low — tracking item, not a build; trigger = first customer complaint or procu...</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>VC Unlimited list pricing is $299 first year, $499/yr after (auto-applied VCFIRSTYEAR coupon delivers Y1 = $299; Y2+ renews at the underlying $499 base). The /pricing tile shows this in the period text ("$299 first year · $499/yr after") at text-base font-medium weight as of 2026-05-23.</t>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1057,98 +1057,14 @@
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. Quality-of-life for sales positioning, not table stakes.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>CCL lab name visual disambiguation in lab switcher</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Open. Cosmetic. Only matters if Lisa reports picking the wrong lab from the dropdown.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>XS (under 1 day)</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Low — cosmetic; only matters if Lisa picks the wrong lab from the dropdown.</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Lisa Veri's two labs both carry "UMass Memorial Health - Milford Regional Medical Center" with the secondary differentiated only by a trailing " CCL" suffix. The NavBar LabSwitcher dropdown truncates long names, which makes fast visual differentiation between her two labs harder than it should be.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab via /api/admin/update-lab.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VC Unlimited Y1/Y2 price disclosure UX</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Open as a tracking item, not a build item. Trigger to act = first customer complaint or first procurement question that suggests the disclosure was missed.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>XS (under 1 day if triggered)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Low — tracking item, not a build; trigger = first customer complaint or procu...</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>VC Unlimited list pricing is $299 first year, $499/yr after (auto-applied VCFIRSTYEAR coupon delivers Y1 = $299; Y2+ renews at the underlying $499 base). The /pricing tile shows this in the period text ("$299 first year · $499/yr after") at text-base font-medium weight as of 2026-05-23.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Pricing rebuild 2026-05-23; flagged at the time as a potential UX gap pending customer feedback.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA.
+---
+_(items #34 and #35 closed 2026-05-24; see C23 and C24 below)_
 ---</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1159,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1928,8 +1844,80 @@
       </c>
       <c r="H23" s="3" t="inlineStr"/>
     </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>XS (under 1 day, actual)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Effort: XS (under 1 day, actual)
+Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
+---</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>XS (under 1 day, actual)</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Effort: XS (under 1 day, actual)
+Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
+---</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H23"/>
+  <autoFilter ref="A1:H25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -670,83 +670,31 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Live QC engine (Levey-Jennings + Westgard)</t>
+          <t>CMS-116 application support + state licensing tracking</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Open. Scoping doc required per Section 8 Process Rules
-("Large tasks: present a build breakdown first, get approval, THEN
-build") before any code.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>XL (6+ weeks; flagship-scale)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>A daily-use QC workflow: Levey-Jennings charts, Westgard
-multi-rule violation detection, control lot management, automated QC
-scheduling. Today VeritaAssure documents QC posture (sign-offs,
-records, retention); it does not run the QC. The COLA segment (small
-physician-office labs, urgent care, ER) lives in daily QC and will
-pick the tool that draws their L-J chart.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Perplexity competitor analysis (myLabCompliance.io),
-2026-05-10. Operator forwarded the analysis; no decision yet.</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA. Multi-week scoping + multi-month
-v1 build. Comparable in scale to VeritaResponse (#17).
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>CMS-116 application support + state licensing tracking</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Open. Small build relative to the other competitor-driven
 candidates. Useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor (myLabCompliance.io) has this; useful at lab startup and...</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CMS-116 is the federal CLIA application form. Today
 VeritaPolicy covers ongoing CLIA posture but not the application
@@ -756,13 +704,13 @@
 CLIA.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io),
 2026-05-10. myLabCompliance.io has this; VeritaAssure does not.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. ~1-2 weeks for v1 (CMS-116 form +
 top-10-state licensure registry).
@@ -770,33 +718,33 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Acquire CAP MOL (Molecular) checklist to verify 2 pending entries</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Open, blocks on operator obtaining the MOL checklist.</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A (operator action — ~1 hour of code work once the file is in hand)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Low — two entries total; low traffic; only matters when a customer cites a MO...</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>PR #108 left 2 entries in server/capRequirements.ts
 flagged as unverified because the operator does not hold the CAP MOL
@@ -810,48 +758,48 @@
 The MOL module's MAS xlsx is the only one missing from that set.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>PR #108 commit 92f9573 (closed via merge 2026-05-11),
 audit findings.</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. Two entries; low traffic.
 ---</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Acquire AABB Standards 35th edition + current COLA Accreditation Manual for exhaustive citation verification</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Open, blocks on operator obtaining the gated accreditor
 manuals. Until then, AABB / COLA citations are best-effort against
 the public-source compilations.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>N/A (operator action — ~1-2 days of audit re-run once the manuals are held)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>High — gates #5 from reaching "exhaustively verified" status for AABB and COLA.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>The 2026-05-11 QC audit found that VeritaScan, cfrRequirements
 cross-refs, and colaRequirements.ts cite about 180 AABB and COLA codes
@@ -871,14 +819,14 @@
  does not enumerate fully.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 QC/QA audit, documented in
 OneDrive\Lab\Regulatory\aaa Truth Master Document\PROVENANCE.md
 "Audit-coverage limits" section.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. Operator-side action item, no code
 work pending until the source documents land.
@@ -886,34 +834,34 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>VeritaStock barcode scanning (full mobile scan flow)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Parked pending first paid commitment.
 ---</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>L (12 working days, ~3 weeks calendar)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>High — strategic moat vs Unity Lab Services ($30K+/yr); presold as included o...</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>The remaining barcode-scanning build for VeritaStock, scoped
 during the 2026-05-20 Pfizer follow-up discussion. Order-now reorder
@@ -922,7 +870,7 @@
 Services-class inventory product.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-05-20 Pfizer follow-up session, after the order-now
 reorder document shipped (PR #286). Strategic decision documented in
@@ -933,31 +881,31 @@
 barcode scanning waits on revenue...</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Plain-language summary layer for verbatim CFR citations</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>M (multi-day content authoring across 96 Master List rows if redesigned corre...</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Medium — director readability win; no customer urgency.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>server/cfrRequirements.ts carries verbatim eCFR text in
 the description field (PR #301 closed #26). The verbatim text is
@@ -966,8 +914,8 @@
 director read faster.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency. Operator
 has not yet authorized a redesign attempt as of 2026-05-21.
@@ -975,29 +923,29 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Lab leader community / forum (paid subscription idea)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>XL (ongoing operational commitment, not a build) as paid; S (a few days to sp...</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Low as paid product (SWOT verdict: don't build); Medium as free lead-funnel a...</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Operator-floated 2026-05-22: a vetted online forum for
 laboratory leaders (directors, managers, supervisors). Pricing as
@@ -1010,51 +958,51 @@
 lab-leader water cooler.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Post-COLA. No customer urgency.
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Active vs view-only seat split</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Open. Real product change, ~1 week of engineering when prioritized. Not blocking any current customer; activate when a prospect explicitly asks "do you charge for our medical director?"</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>M (~1 week of engineering when prioritized)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Medium — quality-of-life for sales positioning; /pricing copy already claims...</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>The pricing analysis doc (2026-05-21 MEDIUM scenario, Decision 3) proposed splitting seats into two types: active (techs, supervisors, lab managers who edit data; counted against the tier seat cap) and view-only (medical director, administrators, reviewers who sign but don't enter; unlimited and free on every tier). The current schema treats all seats as one bucket.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Pricing analysis doc Decision 3 (2026-05-21); deferred during Phase B Stripe wiring (2026-05-23) because no current customer is constrained by the missing distinction.</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA. No customer urgency.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Active vs view-only seat split</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Open. Real product change, ~1 week of engineering when prioritized. Not blocking any current customer; activate when a prospect explicitly asks "do you charge for our medical director?"</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>M (~1 week of engineering when prioritized)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Medium — quality-of-life for sales positioning; /pricing copy already claims...</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>The pricing analysis doc (2026-05-21 MEDIUM scenario, Decision 3) proposed splitting seats into two types: active (techs, supervisors, lab managers who edit data; counted against the tier seat cap) and view-only (medical director, administrators, reviewers who sign but don't enter; unlimited and free on every tier). The current schema treats all seats as one bucket.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Pricing analysis doc Decision 3 (2026-05-21); deferred during Phase B Stripe wiring (2026-05-23) because no current customer is constrained by the missing distinction.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. Quality-of-life for sales positioning, not table stakes.
 ---
@@ -1064,7 +1012,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1075,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1916,8 +1864,44 @@
       </c>
       <c r="H25" s="3" t="inlineStr"/>
     </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
+Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
+---</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H25"/>
+  <autoFilter ref="A1:H26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CMS-116 application support + state licensing tracking</t>
+          <t>VeritaLab™ extension: CMS-116 application support + state licensing registry</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -696,18 +696,25 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CMS-116 is the federal CLIA application form. Today
-VeritaPolicy covers ongoing CLIA posture but not the application
-itself. The form is also relevant at certificate-type changes (waived
-to moderate, moderate to high). State licensing tracking is the
-adjacent piece: many states require their own licensure on top of
-CLIA.</t>
+          <t>VeritaLab already tracks CLIA, state license, and lab
+director license as cert types in the certificate tracker. The
+missing pieces sit alongside that data:
+- CMS-116 form support: the federal CLIA application form. Lab
+ startup workflow and certificate-type changes (waived → moderate,
+ moderate → high) both require filing CMS-116. Today VeritaLab tracks
+ the resulting certificate but does not help author the application.
+- State licensure registry: many states require their own license
+ on top of CLIA. VeritaLab tracks the cert when held; the registry
+ piece is the per-state authority, form URL, fee, and renewal cadence
+ so the lab can look up the state-specific obligation.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io),
-2026-05-10. myLabCompliance.io has this; VeritaAssure does not.</t>
+2026-05-10. myLabCompliance.io has this; VeritaAssure does not.
+Reclassified as a VeritaLab extension 2026-05-25 (operator instinct:
+"it belongs with the VeritaLab module").</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1018,8 +1018,47 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>New module: laboratory non-conforming event documentation</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Parked 2026-05-26 with a one-line scope intent. Michael indicated he will walk through the requirements in more detail in a follow-up conversation. Do not start building until that walkthrough happ...</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>L (initial estimate, pending Michael's scope walkthrough — likely new DB tabl...</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>High — every accredited laboratory (TJC, CAP, COLA, AABB) has to document non...</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Build a module to document laboratory non-conforming events (NCEs). Surfaces a lab needs to capture include specimen rejection, temperature excursions, reagent issues, equipment failures, result-reporting errors, transcription errors, lost specimens, contamination events, and similar quality incidents. Full scope, target accreditor mapping, terminology preference (NCE / NCR / event / incident / occurrence), and how it should relate to the existing VeritaQC corrective-action engine and VeritaResponse deficiency tracker are TBD pending Michael's scope walkthrough.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Post-COLA. No customer urgency yet, but high strategic value once defined — closes a real gap every lab has and that no other Verita module currently serves.
+---</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1057,8 +1057,94 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Marketing one-pager: "Why VeritaCheck" comparative collateral</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering).</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Medium — closes a positioning gap surfaced by six COLA conference attendees a...</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Operator-facing collateral to address conference-attendee feedback that prospects want a VeritaCheck offering equivalent to (or better than) the legacy verification tool many of them use today. Four panels: cost ($25/study or $299/year vs. legacy per-seat licensing), time-to-first-study (minutes, no training), integration (8 study types in one tool plus VeritaPolicy / VeritaScan / VeritaComp in the same suite), compliance (signature-on-page-1 PDFs, real CFR citations, audit log). PDF version for Lisa's email follow-ups and conference leave-behinds; web page version for the marketing site.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Michael confirmed product is substantially better and cheaper; positioning gap is the limiting factor, not the tool.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Post-COLA, conference-driven.
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Screen-capture video: VeritaCheck method comparison in 60 seconds</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering). Pending operator decision on whether to record this themselves or p...</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>S for agent prep (storyboard / pre-fill / captions / checklist); ~1 hour of o...</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Medium — operator selected this as the highest-impact positioning artifact du...</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30-60 second screen recording demonstrating the "experienced lab tech figures it out in seconds" claim. From blank method-comparison study to completed PDF, no voiceover, no narration, visible cursor motion. Embed autoplay-muted on the marketing site, include in conference follow-up emails.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12 conversation. Michael selected the screen-cap video as the highest-impact positioning artifact, then asked the agent to record it. Agent does not have screen-recording capability; option parked rather than fudged.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Post-COLA, conference-driven.
+---</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -986,32 +986,32 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Open. Real product change, ~1 week of engineering when prioritized. Not blocking any current customer; activate when a prospect explicitly asks "do you charge for our medical director?"</t>
+          <t>Open. Foundation PR (step 1) ships in the session that locks the policy; steps 2-6 queue for a daylight multi-PR sprint.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>M (~1 week of engineering when prioritized)</t>
+          <t>M (~1 week of engineering when prioritized; PR 1 foundation lands as a single...</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Medium — quality-of-life for sales positioning; /pricing copy already claims...</t>
+          <t>Medium — closes the gap between /pricing copy and product behavior; sets up s...</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>The pricing analysis doc (2026-05-21 MEDIUM scenario, Decision 3) proposed splitting seats into two types: active (techs, supervisors, lab managers who edit data; counted against the tier seat cap) and view-only (medical director, administrators, reviewers who sign but don't enter; unlimited and free on every tier). The current schema treats all seats as one bucket.</t>
+          <t>Split seats into two types: active (techs, supervisors, lab managers who edit data; counted against the tier seat cap at $500/$425/$333 per seat over the included count) and view-only (medical director or designee, technical consultant, technical supervisor, general supervisor, reviewers who sign but don't enter). Per-tier included counts: Clinic 1, Community 2, Hospital 3; additional view-only seats at $99/yr per seat across all tiers. The current schema treats all seats as one bucket, which contradicts the marketing claim that's already on /pricing.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Pricing analysis doc Decision 3 (2026-05-21); deferred during Phase B Stripe wiring (2026-05-23) because no current customer is constrained by the missing distinction.</t>
+          <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim in favor of capped counts plus add-on.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Post-COLA. Quality-of-life for sales positioning, not table stakes.
+          <t>Post-COLA. Sales positioning gap; will close once the foundation ships.
 ---
 _(items #34 and #35 closed 2026-05-24; see C23 and C24 below)_
 ---</t>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Open. Foundation PR (step 1) ships in the session that locks the policy; steps 2-6 queue for a daylight multi-PR sprint.</t>
+          <t>Done 2026-05-28. Six-PR sequence shipped: #430 foundation (seat_type column, PLAN_VIEW_ONLY_SEATS scaffolding, admin report counts), #431 invite-flow seat_type, #432 dual-cap counting gates, #433 m...</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Post-COLA. Sales positioning gap; will close once the foundation ships.
+          <t>Post-COLA. Sales positioning gap; closed.
 ---
 _(items #34 and #35 closed 2026-05-24; see C23 and C24 below)_
 ---</t>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -663,6 +663,8 @@
         <is>
           <t>Post-COLA. Phase 1 and Phase 2 data layer
 shipped 2026-05-10.
+---
+_(item #22 closed 2026-05-28; see C26 below)_
 ---</t>
         </is>
       </c>
@@ -670,88 +672,30 @@
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VeritaLab™ extension: CMS-116 application support + state licensing registry</t>
+          <t>Acquire CAP MOL (Molecular) checklist to verify 2 pending entries</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Open. Small build relative to the other competitor-driven
-candidates. Useful at lab startup and at certificate-type changes.</t>
+          <t>Open, blocks on operator obtaining the MOL checklist.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>M (1-2 weeks for v1)</t>
+          <t>N/A (operator action — ~1 hour of code work once the file is in hand)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Medium — competitor (myLabCompliance.io) has this; useful at lab startup and...</t>
+          <t>Low — two entries total; low traffic; only matters when a customer cites a MO...</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>VeritaLab already tracks CLIA, state license, and lab
-director license as cert types in the certificate tracker. The
-missing pieces sit alongside that data:
-- CMS-116 form support: the federal CLIA application form. Lab
- startup workflow and certificate-type changes (waived → moderate,
- moderate → high) both require filing CMS-116. Today VeritaLab tracks
- the resulting certificate but does not help author the application.
-- State licensure registry: many states require their own license
- on top of CLIA. VeritaLab tracks the cert when held; the registry
- piece is the per-state authority, form URL, fee, and renewal cadence
- so the lab can look up the state-specific obligation.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Perplexity competitor analysis (myLabCompliance.io),
-2026-05-10. myLabCompliance.io has this; VeritaAssure does not.
-Reclassified as a VeritaLab extension 2026-05-25 (operator instinct:
-"it belongs with the VeritaLab module").</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Post-COLA. ~1-2 weeks for v1 (CMS-116 form +
-top-10-state licensure registry).
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Acquire CAP MOL (Molecular) checklist to verify 2 pending entries</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Open, blocks on operator obtaining the MOL checklist.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>N/A (operator action — ~1 hour of code work once the file is in hand)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Low — two entries total; low traffic; only matters when a customer cites a MO...</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>PR #108 left 2 entries in server/capRequirements.ts
 flagged as unverified because the operator does not hold the CAP MOL
@@ -765,48 +709,48 @@
 The MOL module's MAS xlsx is the only one missing from that set.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>PR #108 commit 92f9573 (closed via merge 2026-05-11),
 audit findings.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Post-COLA. Two entries; low traffic.
 ---</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Acquire AABB Standards 35th edition + current COLA Accreditation Manual for exhaustive citation verification</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Open, blocks on operator obtaining the gated accreditor
 manuals. Until then, AABB / COLA citations are best-effort against
 the public-source compilations.</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A (operator action — ~1-2 days of audit re-run once the manuals are held)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>High — gates #5 from reaching "exhaustively verified" status for AABB and COLA.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>The 2026-05-11 QC audit found that VeritaScan, cfrRequirements
 cross-refs, and colaRequirements.ts cite about 180 AABB and COLA codes
@@ -826,14 +770,14 @@
  does not enumerate fully.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 QC/QA audit, documented in
 OneDrive\Lab\Regulatory\aaa Truth Master Document\PROVENANCE.md
 "Audit-coverage limits" section.</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. Operator-side action item, no code
 work pending until the source documents land.
@@ -841,34 +785,34 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>VeritaStock barcode scanning (full mobile scan flow)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Parked pending first paid commitment.
 ---</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>L (12 working days, ~3 weeks calendar)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>High — strategic moat vs Unity Lab Services ($30K+/yr); presold as included o...</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>The remaining barcode-scanning build for VeritaStock, scoped
 during the 2026-05-20 Pfizer follow-up discussion. Order-now reorder
@@ -877,7 +821,7 @@
 Services-class inventory product.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>2026-05-20 Pfizer follow-up session, after the order-now
 reorder document shipped (PR #286). Strategic decision documented in
@@ -888,31 +832,31 @@
 barcode scanning waits on revenue...</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Plain-language summary layer for verbatim CFR citations</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>M (multi-day content authoring across 96 Master List rows if redesigned corre...</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Medium — director readability win; no customer urgency.</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>server/cfrRequirements.ts carries verbatim eCFR text in
 the description field (PR #301 closed #26). The verbatim text is
@@ -921,8 +865,8 @@
 director read faster.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Post-COLA. No customer urgency. Operator
 has not yet authorized a redesign attempt as of 2026-05-21.
@@ -930,29 +874,29 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Lab leader community / forum (paid subscription idea)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>XL (ongoing operational commitment, not a build) as paid; S (a few days to sp...</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Low as paid product (SWOT verdict: don't build); Medium as free lead-funnel a...</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Operator-floated 2026-05-22: a vetted online forum for
 laboratory leaders (directors, managers, supervisors). Pricing as
@@ -965,10 +909,55 @@
 lab-leader water cooler.</t>
         </is>
       </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Post-COLA. No customer urgency.
+---
+_(item #33 closed 2026-05-28; see C27 below)_
+---
+_(items #34 and #35 closed 2026-05-24; see C23 and C24 below)_
+---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>New module: laboratory non-conforming event documentation</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Parked 2026-05-26 with a one-line scope intent. Michael indicated he will walk through the requirements in more detail in a follow-up conversation. Do not start building until that walkthrough happ...</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>L (initial estimate, pending Michael's scope walkthrough — likely new DB tabl...</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>High — every accredited laboratory (TJC, CAP, COLA, AABB) has to document non...</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Build a module to document laboratory non-conforming events (NCEs). Surfaces a lab needs to capture include specimen rejection, temperature excursions, reagent issues, equipment failures, result-reporting errors, transcription errors, lost specimens, contamination events, and similar quality incidents. Full scope, target accreditor mapping, terminology preference (NCE / NCR / event / incident / occurrence), and how it should relate to the existing VeritaQC corrective-action engine and VeritaResponse deficiency tracker are TBD pending Michael's scope walkthrough.</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Post-COLA. No customer urgency.
+          <t>Post-COLA. No customer urgency yet, but high strategic value once defined — closes a real gap every lab has and that no other Verita module currently serves.
+---
+_(item #37 closed 2026-05-28; see C28 below)_
 ---</t>
         </is>
       </c>
@@ -976,175 +965,48 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Active vs view-only seat split</t>
+          <t>Screen-capture video: VeritaCheck method comparison in 60 seconds</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Done 2026-05-28. Six-PR sequence shipped: #430 foundation (seat_type column, PLAN_VIEW_ONLY_SEATS scaffolding, admin report counts), #431 invite-flow seat_type, #432 dual-cap counting gates, #433 m...</t>
+          <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering). Pending operator decision on whether to record this themselves or p...</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>M (~1 week of engineering when prioritized; PR 1 foundation lands as a single...</t>
+          <t>S for agent prep (storyboard / pre-fill / captions / checklist); ~1 hour of o...</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Medium — closes the gap between /pricing copy and product behavior; sets up s...</t>
+          <t>Medium — operator selected this as the highest-impact positioning artifact du...</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Split seats into two types: active (techs, supervisors, lab managers who edit data; counted against the tier seat cap at $500/$425/$333 per seat over the included count) and view-only (medical director or designee, technical consultant, technical supervisor, general supervisor, reviewers who sign but don't enter). Per-tier included counts: Clinic 1, Community 2, Hospital 3; additional view-only seats at $99/yr per seat across all tiers. The current schema treats all seats as one bucket, which contradicts the marketing claim that's already on /pricing.</t>
+          <t>30-60 second screen recording demonstrating the "experienced lab tech figures it out in seconds" claim. From blank method-comparison study to completed PDF, no voiceover, no narration, visible cursor motion. Embed autoplay-muted on the marketing site, include in conference follow-up emails.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim in favor of capped counts plus add-on.</t>
+          <t>2026-05-12 conversation. Michael selected the screen-cap video as the highest-impact positioning artifact, then asked the agent to record it. Agent does not have screen-recording capability; option parked rather than fudged.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Post-COLA. Sales positioning gap; closed.
----
-_(items #34 and #35 closed 2026-05-24; see C23 and C24 below)_
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>New module: laboratory non-conforming event documentation</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Parked 2026-05-26 with a one-line scope intent. Michael indicated he will walk through the requirements in more detail in a follow-up conversation. Do not start building until that walkthrough happ...</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>L (initial estimate, pending Michael's scope walkthrough — likely new DB tabl...</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>High — every accredited laboratory (TJC, CAP, COLA, AABB) has to document non...</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Build a module to document laboratory non-conforming events (NCEs). Surfaces a lab needs to capture include specimen rejection, temperature excursions, reagent issues, equipment failures, result-reporting errors, transcription errors, lost specimens, contamination events, and similar quality incidents. Full scope, target accreditor mapping, terminology preference (NCE / NCR / event / incident / occurrence), and how it should relate to the existing VeritaQC corrective-action engine and VeritaResponse deficiency tracker are TBD pending Michael's scope walkthrough.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA. No customer urgency yet, but high strategic value once defined — closes a real gap every lab has and that no other Verita module currently serves.
----</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Marketing one-pager: "Why VeritaCheck" comparative collateral</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering).</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Medium — closes a positioning gap surfaced by six COLA conference attendees a...</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Operator-facing collateral to address conference-attendee feedback that prospects want a VeritaCheck offering equivalent to (or better than) the legacy verification tool many of them use today. Four panels: cost ($25/study or $299/year vs. legacy per-seat licensing), time-to-first-study (minutes, no training), integration (8 study types in one tool plus VeritaPolicy / VeritaScan / VeritaComp in the same suite), compliance (signature-on-page-1 PDFs, real CFR citations, audit log). PDF version for Lisa's email follow-ups and conference leave-behinds; web page version for the marketing site.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Michael confirmed product is substantially better and cheaper; positioning gap is the limiting factor, not the tool.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
           <t>Post-COLA, conference-driven.
 ---</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Screen-capture video: VeritaCheck method comparison in 60 seconds</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Open. Re-parked 2026-05-27 (originally PR #117, abandoned with merge conflicts then closed-and-re-authored at current numbering). Pending operator decision on whether to record this themselves or p...</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>S for agent prep (storyboard / pre-fill / captions / checklist); ~1 hour of o...</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Medium — operator selected this as the highest-impact positioning artifact du...</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30-60 second screen recording demonstrating the "experienced lab tech figures it out in seconds" claim. From blank method-comparison study to completed PDF, no voiceover, no narration, visible cursor motion. Embed autoplay-muted on the marketing site, include in conference follow-up emails.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-12 conversation. Michael selected the screen-cap video as the highest-impact positioning artifact, then asked the agent to record it. Agent does not have screen-recording capability; option parked rather than fudged.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Post-COLA, conference-driven.
----</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1155,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2032,8 +1894,116 @@
       </c>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>C26</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>M (1-2 weeks for v1, actual)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Effort: M (1-2 weeks for v1, actual)
+Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
+---</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>C27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Active vs view-only seat split (formerly #33)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
+Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
+---</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
+Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
+---</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H26"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1005,8 +1005,56 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>MediaLab parity hardening (VeritaPolicy approval workflow depth)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Open, customer-triggered. No urgency until a prospect specifically asks for one of the listed depth items.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>L (1-2 weeks for the high-value items; each independent feature is M)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Medium-High — the C29 build shipped the surface MediaLab markets but depth is...</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>The VeritaPolicy approval workflow build (C29, 2026-05-29) hit roughly 60-70% MediaLab feature surface. The following gaps remain when comparing against an enterprise MediaLab Document Control deployment:
+- Quizzes on attestations. Schema columns quiz_score and quiz_total_questions exist on policy_attestations but the quiz authoring + presentation UI was scoped out of Phase 4. MediaLab labs use 5-10 multiple-choice questions per policy to confirm comprehension, not just attestation. Adds compliance defensibility.
+- PDF watermarking. MediaLab burns user name + timestamp into every downloaded PDF copy as a deterrent against forwarding. We serve clean originals. Add Puppeteer-style overlay at download time.
+- Per-policy role mapping at department level. MediaLab lets a lab say "only Microbiology Lab Director can approve Microbiology policies." Our required_role is per-step on the workflow, not per-document-by-manual.
+- Approval delegation. When a reviewer is on vacation, MediaLab supports temporary delegation to a designate. We have no delegation model.
+- In-browser DOCX editing. MediaLab has a structured editor that creates a Table of Contents from headings. We treat documents as...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29 QA pass after C29 shipped (qa-policy-build.js + qa-policy-ui.js: 54/54 happy path verified). Honest depth assessment surfaced by Michael's "how confident are you" question — see C29 entry for full QA receipts.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Post-COLA. Defensive against MediaLab in head-to-head sales calls.
+---</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1017,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2002,8 +2050,44 @@
       </c>
       <c r="H29" s="3" t="inlineStr"/>
     </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>XL (one focused session, 12 PRs landed)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Effort: XL (one focused session, 12 PRs landed)
+Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
+---</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H29"/>
+  <autoFilter ref="A1:H30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1053,8 +1053,88 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>VeritaCheck Accuracy / Bias module: "Simple Accuracy" vs "Method Comparison" mode toggle (Longstreth ask)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Open, sequencing-dependent. Pre- vs post-COLA: indifferent; this is feature work, not pricing or onboarding.
+---</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>M (~half-day: add mode selector to accuracy_bias study type, branch the data-...</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Medium-High. Direct ask from a heavy EP Evaluator user who is otherwise sold...</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Effort: M (~half-day: add mode selector to accuracy_bias study type, branch the data-entry form to a Precision-style replicate grid with per-level target value when "Simple Accuracy" is picked, leave existing multi-instrument correlation flow intact for "Method Comparison" mode).
+Importance: Medium-High. Direct ask from a heavy EP Evaluator user who is otherwise sold on the cal_ver split work. Closes the last conceptual friction point for EP-to-Veritas migrators, which Longstreth flagged as "a big selling point" for transition labs.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Longstreth email reply 2026-06-02 (chat parking-lot turn). Build authorization not yet given.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VeritaQC Import Phase A: human-in-the-loop Gate 3 click-through (deferred)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Open, awaiting Michael's 5-minute click test. Will move task #77 to completed only after he reports the user-visible result.
+---</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>XS (~5 minutes of Michael's time on a live URL).</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Low. Backend contract is fully verified via 35/35 passing offline contract ch...</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Effort: XS (~5 minutes of Michael's time on a live URL).
+Importance: Low. Backend contract is fully verified via 35/35 passing offline contract checks (scripts/verify-veritaqc-import.js) plus three live-API smoke checks against prod (candidates, preview, mappings PUT/GET) on Riverside Regional with seed lot SEED-1780436709094 (18 Glucose results). The browser-driven click was not run because Claude-in-Chrome's renderer froze repeatedly on the Radix Select inside VeritaCheckPage, not on Phase A code itself. Risk of a UX bug surviving to a customer is small but not zero.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>task #77 stalled at Gate 3 step 8 on 2026-06-02. PR #500 squash-merged at commit 17a91ff, prod /api/health confirmed ACTIVE on that commit at 20:43 UTC.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1061,80 +1061,40 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VeritaCheck Accuracy / Bias module: "Simple Accuracy" vs "Method Comparison" mode toggle (Longstreth ask)</t>
+          <t>VeritaQC Import Phase A: human-in-the-loop Gate 3 click-through (deferred)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Open, sequencing-dependent. Pre- vs post-COLA: indifferent; this is feature work, not pricing or onboarding.
+          <t>Open, awaiting Michael's 5-minute click test. Will move task #77 to completed only after he reports the user-visible result.
 ---</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>M (~half-day: add mode selector to accuracy_bias study type, branch the data-...</t>
+          <t>XS (~5 minutes of Michael's time on a live URL).</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Medium-High. Direct ask from a heavy EP Evaluator user who is otherwise sold...</t>
+          <t>Low. Backend contract is fully verified via 35/35 passing offline contract ch...</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Effort: M (~half-day: add mode selector to accuracy_bias study type, branch the data-entry form to a Precision-style replicate grid with per-level target value when "Simple Accuracy" is picked, leave existing multi-instrument correlation flow intact for "Method Comparison" mode).
-Importance: Medium-High. Direct ask from a heavy EP Evaluator user who is otherwise sold on the cal_ver split work. Closes the last conceptual friction point for EP-to-Veritas migrators, which Longstreth flagged as "a big selling point" for transition labs.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Longstreth email reply 2026-06-02 (chat parking-lot turn). Build authorization not yet given.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VeritaQC Import Phase A: human-in-the-loop Gate 3 click-through (deferred)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Open, awaiting Michael's 5-minute click test. Will move task #77 to completed only after he reports the user-visible result.
----</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>XS (~5 minutes of Michael's time on a live URL).</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Low. Backend contract is fully verified via 35/35 passing offline contract ch...</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (~5 minutes of Michael's time on a live URL).
 Importance: Low. Backend contract is fully verified via 35/35 passing offline contract checks (scripts/verify-veritaqc-import.js) plus three live-API smoke checks against prod (candidates, preview, mappings PUT/GET) on Riverside Regional with seed lot SEED-1780436709094 (18 Glucose results). The browser-driven click was not run because Claude-in-Chrome's renderer froze repeatedly on the Radix Select inside VeritaCheckPage, not on Phase A code itself. Risk of a UX bug surviving to a customer is small but not zero.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>task #77 stalled at Gate 3 step 8 on 2026-06-02. PR #500 squash-merged at commit 17a91ff, prod /api/health confirmed ACTIVE on that commit at 20:43 UTC.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1093,8 +1093,48 @@
       </c>
       <c r="H13" s="3" t="inlineStr"/>
     </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Verify-script convention backfill (CLAUDE.md §2)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Open. Pre- vs post-COLA: indifferent.
+---</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>L (8 backfill scripts, each ~2-4 hours, total ~3-5 working days if done as on...</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Medium-High. Procedural-debt cleanup against a NON-NEGOTIABLE convention. CLA...</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Effort: L (8 backfill scripts, each ~2-4 hours, total ~3-5 working days if done as one focused sweep).
+Importance: Medium-High. Procedural-debt cleanup against a NON-NEGOTIABLE convention. CLAUDE.md §2 verify-*.js: every math/logic change ships with a paired script that exercises every meaningful branch. The audit run on 2026-06-02 found 31 of 35 math/logic commits in the last 90 days violated the convention. Some are exempt (renames, citation swaps, copy changes) but at least 8 introduced new math or fixed math defects and should have shipped with verification.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>scripts/audit_verify_script_coverage.py output, run 2026-06-02. Captured as the formal lookback that surfaced the gap.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1133,8 +1133,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr"/>
     </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Outbound demo-invite messaging campaign to 1st-degree LinkedIn contacts</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Parked. Plan documented. Implementation deferred until trigger conditions met.
+---</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>L (1 week prep + 4-6 weeks of staged sends)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>High. Converts existing warm network (~2,500 1st-degree contacts and growing...</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>A staged outbound DM campaign walking Michael's 1st-degree LinkedIn contacts through tier-segmented demo invitations for VeritaAssure. Goal: convert warmest contacts into demo conversations first, then chain into trials and paid subscriptions. Separate pipeline from COLA cohort follow-up and from content-driven inbound; all three feed the same demo funnel but originate from different warmth sources.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04 session, after weekly LinkedIn invite batch completion (80 sent, cap hit at #84 Victoria Allen).</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -581,10 +581,9 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Open. Decision to build = Yes. Sequencing = Decide
-later. User explicitly chose "decide later — just park for now" on
-2026-05-07; will revisit after week of 2026-05-11 once COLA pipeline
-is cleare...</t>
+          <t>BUILT and LIVE (this entry was stale). VeritaResponse shipped as a
+full module: findings table + CRUD + lifecycle, due-date computation, 30/60/90-day
+effectiveness monitoring (wave C3), cross-modu...</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1106,7 +1105,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Open. Pre- vs post-COLA: indifferent.
+          <t>CLOSED 2026-06-13. All 8 high-stakes backfill scripts landed (the
+strike-throughs above); see C30. Pre- vs post-COLA: indifferent.
 ---</t>
         </is>
       </c>
@@ -1172,8 +1172,71 @@
       </c>
       <c r="H15" s="3" t="inlineStr"/>
     </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Wire the two static-audit guards into CI</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>S (half a day)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Medium — each guards a class that produced a real prod-500 / silent-no-op thi...</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Effort: S (half a day)
+Importance: Medium — each guards a class that produced a real prod-500 / silent-no-op this session.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Legacy /api/studies over-returns studies across labs (latent multi-lab footgun)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>S (1-2 days)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Low — not customer-reachable today; the UI uses the lab-scoped paths.
+The le...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Effort: S (1-2 days)
+Importance: Low — not customer-reachable today; the UI uses the lab-scoped paths.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1184,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1242,12 +1305,12 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
+          <t>Verify-script convention backfill (was #41)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1255,13 +1318,16 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
-23 years" as of 2026-05-01.</t>
+          <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
+scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
+EP28 reference interval, Deming/OLS CI, EP15 ANOVA, qualitative method comparison,
+TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>session 299e9a73 turn 14, ~2026-04-28.
+          <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
+landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
@@ -1270,18 +1336,146 @@
     <row r="3" ht="90" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+          <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
+/api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
+existed, so writes fell through to the SPA catch-all (200 + index.html, nothing
+written); the UI did not check the response, so "Add AAA Record" cleared the form
+and looked saved. Confirmed in-browser (rows 20 -&gt; 20), fixed, and prod-verified
+(create adds a row, delete removes it). Also fixed the lab-tagging defect (legacy
+route mis-filed records to the user's default lab on multi-lab accounts).</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-13, found during #18 Phase 3 QA;
+scripts/audit-labscoped-write-routes.mjs now guards the class.
+---</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C32</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>VeritaComp "Unlock assessment" false-success no-op</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
+/api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
+It had been registered at the non-:labId path while using labScopeMiddleware (which
+400s without :labId), so the client's lab-scoped POST hit the SPA fallback (200),
+and the client's if (!res.ok) showed a false "Assessment unlocked" toast while the
+signed assessment stayed locked. Prod-verified (path now returns JSON 404, not SPA
+HTML).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
+---</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>C33</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
+widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
+longest lab name. PRs #751/#752 fixed 6 delete handlers that 500'd on foreign-key
+constraints (VeritaCheck verification analytes; VeritaResponse finding effectiveness
+checks, in BOTH the lab-scoped and legacy handlers; VeritaMap instrument staff links;
+competency assessment element docs; competency quiz assignments). All prod-verified
+500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
+---</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
+23 years" as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 14, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1294,7 +1488,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1302,109 +1496,109 @@
 ---</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: site-wide search confirmed all surveyor language
 is past-tense, consistent with user's 2021-2025 service. User closed
 the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
 /api/my-studies/export. server/routes.ts line 1491 implements the
 endpoint. Pulled forward into pre-COLA per user instruction.</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 5, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: no ghp_* or github_pat_* patterns in current
 SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -1413,29 +1607,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -1446,30 +1640,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -1479,59 +1673,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -1546,29 +1740,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -1576,29 +1770,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -1613,56 +1807,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -1680,64 +1874,64 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
 features the Perplexity competitor analysis identified as a gap:</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the feature set ships today.
 ---</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>PAL studies guided workflow (formerly #23)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: VeritaCheck™ already ships the Precision /
 Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Originally Perplexity competitor analysis 2026-05-10.
 Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
@@ -1745,23 +1939,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
@@ -1769,29 +1963,29 @@
 shipped:</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -1802,7 +1996,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -1810,23 +2004,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -1837,7 +2031,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -1845,23 +2039,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -1872,7 +2066,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -1881,23 +2075,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -1910,7 +2104,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -1919,30 +2113,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -1951,262 +2145,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H30"/>
+  <autoFilter ref="A1:H34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/PARKING_LOT.xlsx
+++ b/PARKING_LOT.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETIRED" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OPEN'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLOSED'!$A$1:$H$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RETIRED'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1172,71 +1172,8 @@
       </c>
       <c r="H15" s="3" t="inlineStr"/>
     </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Wire the two static-audit guards into CI</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>S (half a day)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Medium — each guards a class that produced a real prod-500 / silent-no-op thi...</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Effort: S (half a day)
-Importance: Medium — each guards a class that produced a real prod-500 / silent-no-op this session.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Legacy /api/studies over-returns studies across labs (latent multi-lab footgun)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>S (1-2 days)</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Low — not customer-reachable today; the UI uses the lab-scoped paths.
-The le...</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Effort: S (1-2 days)
-Importance: Low — not customer-reachable today; the UI uses the lab-scoped paths.</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1247,7 +1184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1305,12 +1242,12 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Verify-script convention backfill (was #41)</t>
+          <t>Wire the two static-audit guards into CI (was #43)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1318,36 +1255,92 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>Closure evidence: both guards wired into the Multi-Lab Mutations Audit CI
+workflow (.github/workflows/multilab-mutations-audit.yml) as steps:
+audit-delete-cascades.mjs (DELETE handlers that orphan non-cascade FK children)
+and audit-labscoped-write-routes.mjs (client lab-scoped writes with no matching
+server route). Both exit non-zero on a finding, failing the job. Confirmed 0
+findings on main at closure. Closed 2026-06-14. NOTE: a hard merge-block still
+needs the one-time branch-protection toggle for the "multilab-mutations" check
+(same caveat as the existing guards already in that workflow).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>C35</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Legacy /api/studies over-returns studies across labs (was #44)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: GET /api/studies now scopes its list to the active lab
+when one is resolved from the Referer (server/routes.ts), so every returned row
+opens on the lab-scoped detail page; the genuine no-active-lab legacy global
+fallback is unchanged. drizzle's studies schema lacks lab_id, so the scope filter
+resolves the lab's study ids via raw SQL (idx_studies_lab_id) and filters on id,
+mirroring the /api/labs/:labId/studies handler. Closed 2026-06-14.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Verify-script convention backfill (was #41)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Closure evidence: all 8 high-stakes math/logic commits now ship a paired
 scripts/verify-*.js (EP17 sensitivity, Deming lot-to-lot, CUMSUM+QC+multi-analyte,
 EP28 reference interval, Deming/OLS CI, EP15 ANOVA, qualitative method comparison,
 TEa boundary), per the strike-throughs in #41. Closed 2026-06-13.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>scripts/audit_verify_script_coverage.py lookback, 2026-06-02; backfills
 landed 2026-06-03..06.
 ---</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>VeritaPT AAA create/update/delete silently no-op in the multi-lab UI</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #754 (commit 92ad499) added lab-scoped POST/PUT/DELETE
 /api/labs/:labId/pt/aa-records. The UI posted to the lab-scoped path but only GET
@@ -1358,30 +1351,30 @@
 route mis-filed records to the user's default lab on multi-lab accounts).</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>2026-06-13, found during #18 Phase 3 QA;
 scripts/audit-labscoped-write-routes.mjs now guards the class.
 ---</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>C32</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>VeritaComp "Unlock assessment" false-success no-op</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #755 (commit 4234007) moved the unlock route to
 /api/labs/:labId/competency/assessments/:id/unlock (the path the client calls).
@@ -1392,29 +1385,29 @@
 HTML).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-06-13, found by scripts/audit-labscoped-write-routes.mjs.
 ---</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>C33</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>FK-cascade delete 500s + NavBar laptop-width overflow</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PRs #749/#750 fixed NavBar horizontal overflow at laptop
 widths (collapse to the hamburger below 1560px); prod-verified at 1280-1920 with the
@@ -1425,57 +1418,57 @@
 500 -&gt; 200. scripts/audit-delete-cascades.mjs guards the class.</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>2026-06-13 browser QA of the A7-D4 wave + retro-QC of the 72h PR window.
 ---</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>FAQ "over 25 years" -&gt; "over 23 years"</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/FAQPage.tsx line 20 reads "over
 23 years" as of 2026-05-01.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>session 299e9a73 turn 14, ~2026-04-28.
 ---</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>David's VeritaQA grey-button bug (seat permissions mode)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #10 squash-merged as commit a43fbba on
 2026-05-01 23:19 MST. Railway deploy succeeded; deployed bundle
@@ -1488,7 +1481,7 @@
 against his exact stored shape (14 of 14 expected outcomes matched).</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>2026-05-01 David's report; veritabench + veritastock
 weren't in MODULE_LIST so seat permissions silently defaulted to
@@ -1496,75 +1489,17 @@
 ---</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>TeamPage present-tense "TJC surveyor" check</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: site-wide search confirmed all surveyor language
-is past-tense, consistent with user's 2021-2025 service. User closed
-the item in session 299e9a73 turn 4.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>session 299e9a73, ~2026-04-28.
----</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>My Studies CSV/XLSX export (John as design partner)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
-/api/my-studies/export. server/routes.ts line 1491 implements the
-endpoint. Pulled forward into pre-COLA per user instruction.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>session 299e9a73 turn 5, ~2026-04-28.
----</t>
-        </is>
-      </c>
       <c r="H9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+          <t>TeamPage present-tense "TJC surveyor" check</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -1572,8 +1507,9 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
-SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+          <t>Closure evidence: site-wide search confirmed all surveyor language
+is past-tense, consistent with user's 2021-2025 service. User closed
+the item in session 299e9a73 turn 4.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1587,18 +1523,75 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+          <t>My Studies CSV/XLSX export (John as design partner)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: client/src/pages/DashboardPage.tsx line 46 calls
+/api/my-studies/export. server/routes.ts line 1491 implements the
+endpoint. Pulled forward into pre-COLA per user instruction.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>session 299e9a73 turn 5, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Rotate GitHub PAT (because old PAT was committed in SESSION_HANDOFF files)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Closure evidence: no ghp_* or github_pat_* patterns in current
+SESSION_HANDOFF.md or SESSION_HANDOFF-2.md as of 2026-05-01.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>session 299e9a73, ~2026-04-28.
+---</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>VeritaPolicy service-line filtering removed (formerly #4)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Closure rationale (operator decision 2026-05-10): Keep all
 VeritaPolicy rows. CFR-only references with no accreditor reference
@@ -1607,29 +1600,29 @@
 report misread the design intent.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>CLIA number format validation (formerly #13)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: shared/validateClia.ts defines CLIA_REGEX =
 /^\d{2}D\d{7}$/ (line 24), validateClia() helper with whitespace
@@ -1640,30 +1633,30 @@
 shape exists and behaves as specified.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>VeritaMap lab-wide menu toggle (formerly #19)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/VeritaMapLabwidePage.tsx
 exists and implements the labwide read-only union view. Route is
@@ -1673,59 +1666,59 @@
 parking lot plan (read-only union view, per-session toggle) shipped.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Agent verification 2026-05-10 via grep + file read.
 Operator confirmed shipped 2026-05-10.
 ---</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Tier-1 smoke test checklist (formerly #6)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: docs/smoke-test-tier1.md documents the Tier-1
 smoke-test process and post-deploy verification steps. Shipped via
 PR #81 as part of the 2026-05-10 wave.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Per-module gating (formerly #7)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Client-side useIsReadOnly module keys wired
 on client/src/pages/VeritaPolicyAppPage.tsx and
@@ -1740,29 +1733,29 @@
 PR #76.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>VeritaStock shipped copy (formerly #8)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: client/src/pages/ArticleInventoryManagementPage.tsx
 line 305 footer reads "platform that includes VeritaStock™" instead
@@ -1770,29 +1763,29 @@
 on /resources/laboratory-inventory-management. Shipped via PR #75.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Admin report one-row-per-lab (formerly #14)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: /api/admin/report rewritten in
 server/routes.ts (~line 595) to LEFT JOIN labs on
@@ -1807,56 +1800,56 @@
 prerequisite, not a code bug). Shipped via PR #85.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>UI relabel "CLIA TEa" -&gt; "Lab-Set Internal Goal" (formerly #1)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped across four PRs over 2026-05-10.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
 ---</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>WSLH PT vendor (formerly #15)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: Shipped 2026-05-10 via PR #79 (merge commit
 eeebc6e; merged after rebase to resolve a server/db.ts collision
@@ -1874,68 +1867,9 @@
 'WSLH' is the post-deploy success signal. Shipped via PR #79.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Operator instruction 2026-05-10 in this session.
----</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
-features the Perplexity competitor analysis identified as a gap:</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the feature set ships today.
----</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>PAL studies guided workflow (formerly #23)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Closure evidence: VeritaCheck™ already ships the Precision /
-Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Originally Perplexity competitor analysis 2026-05-10.
-Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
-full.
 ---</t>
         </is>
       </c>
@@ -1944,12 +1878,12 @@
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+          <t>VeritaStock lot tracking + expiration + reorder alerts (formerly #21)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
@@ -1957,35 +1891,94 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>Closure evidence: VeritaStock™ shipped the bench-level inventory
+features the Perplexity competitor analysis identified as a gap:</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the feature set ships today.
+---</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>PAL studies guided workflow (formerly #23)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Closure evidence: VeritaCheck™ already ships the Precision /
+Accuracy / Linearity (PAL) study set under EP-protocol naming:</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Originally Perplexity competitor analysis 2026-05-10.
+Audit 2026-05-21 confirmed the EP studies cover the PAL framing in
+full.
+---</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Source-grounded 21/29/45 CFR + 42 CFR 482-485 (formerly #26)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Closure evidence: PR #301 (commit 8c27806, merged 2026-05-21)
 source-grounded the 74 remaining non-493 entries in
 server/cfrRequirements.ts against verbatim eCFR XML. Breakdown
 shipped:</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>PR #301; tasks #18 in the in-session task tracker.
 ---</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>VeritaPolicy "Non CLIA" chapter rename (formerly #3)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: PR #300 (commit 34d7707, merged 2026-05-21)
 renamed all 44 user-facing chapter labels in
@@ -1996,7 +1989,7 @@
 page.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>CAP customer screenshot of the /veritapolicy chapter
 headers, 2026-05-01 evening. PR #300; tasks #17 in the in-session
@@ -2004,23 +1997,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>VeritaStock department-scope toggle (formerly #31)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #319 (commit d01f5fe, merged 2026-05-22)
 shipped the persistent dept-scope toggle on VeritaStockPage. A new
@@ -2031,7 +2024,7 @@
 workspace without re-filtering.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>John, San Carlos lab, 2026-05-21. Same conversation that
 drove the vendor dropdown (PR #304), FILTERED VIEW banner (PR #305),
@@ -2039,23 +2032,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Primary-lab seat counting (formerly #12)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: is_primary_lab INTEGER NOT NULL DEFAULT 0
 column was added to the lab_members table at db.ts:1276, with the
@@ -2066,7 +2059,7 @@
 is_primary_lab=1 ordering).</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion. Build shipped as part
 of the Multi-Lab Tier 2 architecture work (Phase 3.x series, prior
@@ -2075,23 +2068,23 @@
 ---</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Multi-lab pricing model — Option A (formerly #11)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Closure evidence: PR #322 (commit 0ccd925, merged 2026-05-22)
 added the customer-facing line to the pricing page that reflects
@@ -2104,7 +2097,7 @@
 Enterprise+ block, reads:</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2026-05-07 multi-lab discussion (Lisa Veri's
 canonical-case session). PR #322 (initial build); softening PR
@@ -2113,30 +2106,30 @@
 ---</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>VeritaOps cost-per-test module (formerly #10)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Closure evidence: v1 of the VeritaOps Cost-Per-Reportable-Test
 (CPRT) module shipped across PR #325 through PR #330 on 2026-05-22.
 The module is feature-complete for the typical lab director workflow.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>This thread, 2026-05-07 12:05 PM CDT, user message:
 "Parking lot: build an operations module for cost per test
@@ -2145,262 +2138,262 @@
 ---</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>CCL lab name visual disambiguation in lab switcher (formerly #34)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from...</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low — cosmetic; only mattered when Lisa or Michael picked the wrong lab from the dropdown.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>flagged 2026-05-23 immediately after provisioning Lisa's CCL lab; closed 2026-05-24.
 ---</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>VC Unlimited Y1/Y2 price disclosure UX (formerly #35)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>XS (under 1 day, actual)</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Low when shipped (proactive, no customer complaint yet) — but high if a procu...</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Effort: XS (under 1 day, actual)
 Importance: Low when shipped (proactive, no customer complaint yet) — but high if a procurement reviewer later disputes the $499 renewal as undisclosed.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Pricing rebuild 2026-05-23; closed 2026-05-24 proactively before any customer dispute.
 ---</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>VeritaQC Phase 1 (Levey-Jennings + Westgard live engine) (formerly #20)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B...</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>High — largest single gap vs myLabCompliance.io per Perplexity competitor ana...</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Effort: L (about 5 days end-to-end, actual: Phase 0 schema → Phase 1A evaluator → 1B entry UI → 1C daily review → 1D monthly PDF + attestation)
 Importance: High — largest single gap vs myLabCompliance.io per Perplexity competitor analysis; promotes VeritaAssure from documentation tool to lab operations platform.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis 2026-05-10. Scoping confirmed via the build_phase1_mockup.py iterations 2026-05-24. Shipped 2026-05-25.
 ---</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>VeritaLab CMS-116 application support + state licensing registry (formerly #22)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>M (1-2 weeks for v1, actual)</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Medium — competitor parity (myLabCompliance.io) plus useful at lab startup an...</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Effort: M (1-2 weeks for v1, actual)
 Importance: Medium — competitor parity (myLabCompliance.io) plus useful at lab startup and at certificate-type changes.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Perplexity competitor analysis (myLabCompliance.io), 2026-05-10. Reclassified as a VeritaLab extension 2026-05-25. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Active vs view-only seat split (formerly #33)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>M (~1 week of engineering, actual: shipped in a single multi-PR session)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Medium — closed the gap between /pricing copy and product behavior; gives sal...</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Effort: M (~1 week of engineering, actual: shipped in a single multi-PR session)
 Importance: Medium — closed the gap between /pricing copy and product behavior; gives sales a clean answer for "do you charge for our medical director?"</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Pricing analysis doc Decision 3 (2026-05-21); MEDIUM scenario revised 2026-05-29 to retire the "unlimited view-only" claim. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>"Why VeritaCheck" comparative one-pager (formerly #37)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>S (one design pass + four claim paragraphs + PDF + matching marketing-site pa...</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Medium — closed a positioning gap surfaced by six COLA conference attendees a...</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Effort: S (one design pass + four claim paragraphs + PDF + matching marketing-site page, actual)
 Importance: Medium — closed a positioning gap surfaced by six COLA conference attendees attached to a legacy verification tool; converts product-quality advantage into a leave-behind Lisa can hand out.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>2026-05-11 / 2026-05-12 conference notes review with Michael. Conference attendees (Whitehead, Odegard, Othman, Molinelli, Kyle, Allred) expressed interest in equivalent / superior product. Shipped 2026-05-28.
 ---</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>VeritaPolicy approval workflow — MediaLab functional mirror</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>XL (one focused session, 12 PRs landed)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>High — replaces MediaLab Document Control ($752/$2,250 starting price, scalin...</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Effort: XL (one focused session, 12 PRs landed)
 Importance: High — replaces MediaLab Document Control ($752/$2,250 starting price, scaling to $10K-$20K/yr at enterprise per Capterra public data) with an included VeritaPolicy feature; closes a real positioning gap and gives sales a direct comparator line.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Pricing strategy conversation 2026-05-29 (Michael: "I don't like bolt-ons; we should replicate this") → scoped 8 phases → shipped all 12 PRs in single session. Shipped 2026-05-29.
 ---</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H34"/>
+  <autoFilter ref="A1:H36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
